--- a/internal_doc/05.测试设计/驱动测试/C++驱动/C++驱动测试设计.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/C++驱动/C++驱动测试设计.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="730" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="730" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="13" r:id="rId1"/>
     <sheet name="测试设计" sheetId="21" r:id="rId2"/>
     <sheet name="sdb" sheetId="5" r:id="rId3"/>
-    <sheet name="sdbCollectionSpace" sheetId="14" r:id="rId4"/>
-    <sheet name="sdbCollection" sheetId="4" r:id="rId5"/>
-    <sheet name="sdbCursor" sheetId="7" r:id="rId6"/>
-    <sheet name="sdbNode" sheetId="9" r:id="rId7"/>
-    <sheet name="sdbReplicaGroup" sheetId="6" r:id="rId8"/>
-    <sheet name="sdbDomain" sheetId="15" r:id="rId9"/>
+    <sheet name="sdbDomain" sheetId="15" r:id="rId4"/>
+    <sheet name="sdbCollectionSpace" sheetId="14" r:id="rId5"/>
+    <sheet name="sdbCollection" sheetId="4" r:id="rId6"/>
+    <sheet name="sdbCursor" sheetId="7" r:id="rId7"/>
+    <sheet name="sdbNode" sheetId="9" r:id="rId8"/>
+    <sheet name="sdbReplicaGroup" sheetId="6" r:id="rId9"/>
     <sheet name="sdbLob" sheetId="12" r:id="rId10"/>
     <sheet name="other" sheetId="17" r:id="rId11"/>
   </sheets>
@@ -55,122 +55,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-静态库</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>动态库</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>空指针</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-暂时无法测试</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-析构释放连接，获取多个游标后直接断开连接，对象析构顺序</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -181,55 +65,12 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E7" authorId="0">
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-OID </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>非</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>OID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
+            <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
@@ -239,38 +80,40 @@
         </r>
         <r>
           <rPr>
-            <sz val="8"/>
+            <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-大数据量批插</t>
+密码：空指针，空串，普通字符串</t>
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="8"/>
+            <sz val="9"/>
             <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>Author:</t>
         </r>
         <r>
           <rPr>
-            <sz val="8"/>
+            <sz val="9"/>
             <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-hint queryAndUpdate queryAndRemove</t>
+要检查结果，确认执行生效</t>
         </r>
       </text>
     </comment>
@@ -279,13 +122,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="476">
   <si>
     <t>接口名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -876,11 +715,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>INT32 attachCollection ( const CHAR *subClFullName,
-                         const bson::BSONObj &amp;options)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>INT32 explain ( sdbCursor &amp;cursor,
                 const bson::BSONObj &amp;condition = _sdbStaticObject,
                 const bson::BSONObj &amp;select    = _sdbStaticObject,
@@ -1571,44 +1405,1191 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>taskID小于等于0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口测试主要是测试C++驱动中的各个类的接口功能是否正常，主要验证两大操作：数据库操作和集群操作。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼容性测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别在windows linux上执行测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证所有测试用例和samples</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大小端测试（暂时无法测试）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动库测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别验证链接静态库 动态库执行测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT32 getQueryMeta ( sdbCursor &amp;cursor,
+                     const bson::BSONObj &amp;condition,
+                     const bson::BSONObj &amp;orderBy,
+                     const bson::BSONObj &amp;hint,
+                     INT64 numToSkip,
+                     INT64 numToReturn )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上（OnlyAttach改成OnlyDetach）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口测试重点：1、验证接口正常的功能（覆盖默认值参数校验）
+             2、参数校验：指针类型参数检查空指针，字符串类型参数校验空串，vector类型参数检验空vector，数组长度参数校验小于等于0
+                         集合空间名 集合名 数据组名 域名校验最大长度127
+                         经过驱动处理的参数进行校验，覆盖驱动参数处理的每一个分支
+             3、与sdb shell对应的接口比较，检查多余的参数
+             4、验证sdb shell中不存在的接口的功能( resetSnapshot/getQueryMeta/Lob )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、验证正常功能测试时没有内存泄露
+2、验证并发测试时无内存泄露
+3、验证大小端测试时没有内存泄露
+4、验证samples中的内存泄露
+5、验证获取多个游标后，不使用接口断开连接，使用析构断开连接时的资源泄露</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常功能测试：测试接口的正常功能
+异常功能测试：连接断开后执行操作
+             对象未创建执行操作
+             对象关闭后执行操作（游标Lob）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C++驱动测试设计
+C++驱动的主要功能是与数据库引擎进行通信，一般的流程是校验传入参数后构造消息发送到引擎端，然后接收引擎返回的消息进行解析返回结果给客户端。对于C++驱动接口的测试主要针对接口的功能和参数校验进行测试。由于同一个连接上的对象共用套接字（驱动无锁），不能对同一个连接上的对象进行并发操作，连接之间没有共用的资源，不做并发测试。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT32 connect ( const CHAR *pHostName,
+                 const CHAR *pServiceName )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用connect( pHostName, port, "", "")</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用connect( pHostName, pServiceName, "", "")</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.将pServiceName转换为端口号，服务名转换，转换数字
+2.调用connect( pHostName, port, pUsrName, pPasswd)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.空指针检查
+2.密码转换md5
+3.构造删除鉴权消息并发送，接收返回消息，检查返回消息有效性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.如果scoket还存在，则断开（构造连接断开消息并发送，关闭并释放scoket）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.将listType映射为对应的命令
+2.构造查询消息并发送，接收并检查返回消息
+3.构造cursor对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开后获取cs
+空指针 cs名长度超过127
+创建cs并获取 获取不存在的cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查socket
+2.检查空指针 cs名长度
+3.从本地缓存中获取cs，如果获取失败则从服务端获取(runCommand)，并新建缓存插入
+4.构造cs对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs名字长度超过127 空指针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cs名字长度（未检查空指针）
+2.构造bson，加入csname字段，再加入options的所有字段
+2.runCommand（消息构造发送接收检查）
+3.构造cs对象
+4.插入缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cs名字长度（未检查空指针）
+2.runCommand（消息构造发送接收检查）
+3.构造cs对象
+4.插入缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pServiceName验证服务名/端口/空指针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pConnAddrs中的地址没有使用:分割主机名 端口号/空指针
+arrSize取值为0或负数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cs名字长度
+2.构造bson，加入cs名字
+3.runCommand
+4.删除缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs名字长度超过127 空指针
+删除cs后获取cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">调用getList </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针
+2.使用rgname构造cond，然后调用getList
+3.获取游标中的第一个元素，使用元素内容构造rg对象( rgname rgid db isCatalog ）
+4.如果游标为空，返回失败</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+获取不存在的rg
+获取数据组 编目组，检查组信息（组名 组ID 是否编目组）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用id构造cond，调用getList
+2.以下步骤同上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取不存在的rg
+获取数据组 编目组，检查组信息（组名 组ID 是否编目组）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查rgname长度
+2.runCommand
+3.构造rg对象返回，将rg添加到db的set中（注册）（cs cl操作中没有注册操作）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rg名长度超过127 空指针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 检查长度=0 &gt;127
+2.runCommand （没有反注册操作）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rg名长度等于0 超过127 空指针
+使rg先于db进行析构</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针
+2.构造bson，加入hostname svcname dbpath，再加入config的各个字段，config中的字段与前面参数重复时跳过这些字段
+3.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+config中包含了hostname svcname dbpath且与前面参数不一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查rgname长度
+2.构造bson，加入rgname
+3.runCommand
+4.构造rg对象，注册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查sql语句合法性（第一个非空字符是否是s S l L）
+2.构造sql消息
+3.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+sql语句不合法（字符串以s S l L开头）
+合法的sql更新语句应该是update …</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查sql语句合法性（第一个非空字符是否是s S l L）
+2.构造sql消息
+3.发送 接收 解析 检查消息
+4.构造cursor对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+sql语句不合法（字符串不以s S l L开头）
+合法的sql查询语句应该是select .. 或 list ..</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.构造开始事务消息
+2.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.构造提交事务消息
+2.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.构造回滚事务消息
+2.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.构造查询消息
+2.发送 接收 解析 检查消息（可以使用runCommand）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用spname构造bson
+2.构造查询消息
+3.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针
+2.使用code构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用code构造bson
+2.构造查询消息
+3.发送 接收 解析 检查消息
+4.构造cursor对象
+5.检查返回消息的返回个数 长度等，给type赋值（errmsg无用参数）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用options构造bson（多余的拷贝）
+2.构造查询消息
+3.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上
+最后构造cursor返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上 不需要构造cursor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 检查num &lt; 0
+2.使用taskIDs构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+num小于等于0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查taskID&lt;=0
+2.使用taskID构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options为空对象
+options的第一个字段不是PreferInstance
+options中的PreferInstance的值非法或者类型非法
+合法值m M s S a A 1-7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查options是否为空
+2.找到options的第一个字段，检查是否是PreferInstance，并且字段值是否合法，使用该字段构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.构造杀死所有上下文的消息并发送
+2.将连接的游标lob清空，各个游标lob对象上的连接置为NULL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查socket是否存在 是否连接状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未创建的连接对象检查有效性
+创建连接后检查有效性
+断开连接后检查有效性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针 domain名长度&gt;127</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 domain名长度
+2.构造bson 加入domainname
+3.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 domain名长度
+2.构造bson 加入domainname和options
+3.runCommand
+4.构造domain对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 domain名长度
+2.构造bson 加入domainname
+3.调用getList，加入bson作为匹配条件
+4.从游标中获取结果，构造domain对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针 domain名长度&gt;127
+获取不存在的domain
+获取存在的domain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用getList(hint无用参数)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UINT64 getLastAliveTime() const</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回成员变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用主机名 端口号创建scocket连接（如果socket已连接，则断开重连）；设置socket属性（disableNagle keepalive keepidle keepinterval keepcount）；如果使用ssl，并且有宏定义，使用ssl连接
+2.获取服务端系统信息（判断大小端）
+3.密码字符串转换为md5
+4.构造鉴权消息发送，接收返回消息并校验（校验返回消息的opCode与发送消息的opCode是否对应，大小端转换）（消息构造的流程：计算消息包需要的4字节对齐长度，分配buffer，将消息内容按消息格式按4字节对齐拷贝入buffer中，大小端转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+密码：检查空串 普通字符串
+重复连接
+服务端关闭后检查连接有效性（节点正常重启，异常重启）（检查socket）
+开启SSL进行连接（驱动未开启SSL宏）
+客户端 服务端分别为大端 小端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查参数 空指针检查 arrSize&lt;=0
+2.循环获取地址数组内的随机值，将地址按:分隔成主机名和端口号，调用connect( pHostName, pServiceName, pUsrName, pPasswd )进行连接，当连接成功后退出返回连接成功，或者两次循环产生相同的随机值时退出返回连接失败</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查参数 空指针检查
+2.密码转换为md5
+3.构造鉴权消息并发送，接收返回消息，检查返回消息有效性（opCode）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复断开连接
+服务端断开连接时执行disconnect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.将snapType映射为对应的命令(switch)
+2.构造查询消息并发送，接收检查返回消息
+3.构造cursor对象并返回（设置cursor的成员值）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>断开连接后执行
+清空快照后检查快照信息是否清0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查socket是否连接
+2.检查空指针 集合全名长度
+3.从本地缓存中获取集合，如果获取失败则发送查询消息到服务端获取集合(runCommand)，并将集合插入缓存中（缓存为一个哈希表，表内每个节点存储名字和时间）
+4.构造cl对象并返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+执行返回不同类型结果的js语句</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查socket是否连接
+2.构造查询消息并发送，接收并检查返回消息（调用runCommand）（runCommand用于处理查询消息）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 cl名长度
+2.检查cs名 连接，拼接cl全名
+3.从本地缓存获取cl，获取失败时构造cl全名bson从服务端获取，插入新建缓存
+4.构造cl对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用createCollection( pCollection, _staticObj, collection )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针 cl名长度&gt;127
+cs对象未创建 连接断开
+创建cl后获取cl
+获取不存在的cl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 cl名长度
+2.检查cs名 连接，拼接cl全名
+3.使用cl全名和options构造bson
+4.runCommand
+5.构造cl对象 插入新建缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针 cl名长度
+2.检查cs名 连接，拼接cl全名
+3.runCommand
+4.删除缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回成员对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用cl全名构造bson, runCommand
+2.更新缓存
+3.从游标中获取结果返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查空指针 空串
+3.将cl全名和参数构造成bson
+4.构造查询消息
+5.发送 接收 解析 检查消息
+6.更新本地缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查空指针 空串
+3.检查百分比
+3.将cl全名和参数构造成bson
+4.构造查询消息
+5.发送 接收 解析 检查消息
+6.更新本地缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针 cl名长度&gt;127
+cs对象未创建 连接断开
+过程中连接断开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查空指针 空串
+3.使用cl全名 参数 isAsync构造bson
+4.构造查询消息
+5.发送 接收 解析 检查消息
+6.更新缓存
+7.从游标中获取taskID返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上（参数检查增加检查百分比的步骤）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.根据options中是否有Alter字段分别转入两个函数进行处理（文档中没有Alter字段，不测有Alter字段的分支）
+2.转入函数中，检查cl全名 连接
+3.runCommand
+4.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查vector大小 &lt;=0时直接跳出
+3.判断每条记录，没有oid时加入oid
+4.将所有记录构造为一条插入消息
+5.发送 接收 解析 检查消息
+6.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查记录是否需要加入oid
+3.构造插入消息
+4.发送 接收 解析 检查消息
+5.更新缓存
+6.返回oid值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+记录有oid 
+记录无oid
+插入后查询记录检查oid是否正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.调用内部函数_update
+2.检查cl全名 连接
+3.构造更新消息
+4.发送 接收 解析 检查消息
+5.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+flags覆盖所有取值和一个非法值
+vector为空数组
+vector内的记录部分有oid 部分无oid
+插入后查询检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+flags覆盖所有取值和一个非法值
+更新后查询检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.将setOnInsert和hint合并为一个新hint
+2.调用_update</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>setOnInsert分别为默认值，不为默认值，检查upsert结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.构造删除消息
+3.发送 接收 解析 检查消息
+4.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+删除后检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.调用函数调整flag（实际未修改）
+3.如果numToReturn为1，flag与FLG_QUERY_WITH_RETURNDATA做或运算（置位）
+4.runCommand
+5.更新缓存
+6.检查游标，如果为NULL则构造一个空游标返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+flag覆盖所有取值和一个非法值
+numToReturn取值为1（与flag组合验证）
+查询不存在的记录
+查询存在的记录 检查查询结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.调用query
+2.检查query返回的游标，获取记录返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询存在的记录
+查询不存在的记录 检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.调用内部函数_queryAndModify
+2.将remove操作名 是否remove合并成一个modify的bson，将hint和modify合并成一个bson
+3.flag值与FLG_QUERY_MODIFY做或运算
+4.调用query</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上调用内部函数_createIndex，sortBufferSize取值为传入参数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.调用内部函数_createIndex，sortBufferSize取值为默认值（64M）
+2.检查cl全名 连接
+3.检查sortBufferSize&lt;0
+4.将参数构造成bson
+5.构造查询消息
+6.发送 接收 解析 检查消息
+7.更新缓存
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sortBufferSize &lt; 0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.如果pName不为NULL，构造cond的sbson
+3.使用cl全名构造bson
+4.构造查询消息
+5.发送 接收 解析 检查消息
+6.更新缓存
+7.构造cursor返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名 index名构造bson 
+3.构造查询消息
+4.发送 接收 解析 检查消息
+5.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 空串
+检查索引是否创建
+使用索引查询检查访问计划</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 空串
+检查返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 空串
+删除索引后获取索引检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回成员变量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用obj构造聚集消息
+3.发送 接收 解析 检查消息
+4.更新缓存
+5.构造cursor返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+obj为空
+检查聚集返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息
+5.更新缓存
+6.构造cursor返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+检查返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接 空指针 subcl名长度
+2.使用cl全名 subcl名 options构造bson
+3.构造查询消息
+4.发送 接收 解析 检查消息
+5.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 subcl名长度&gt;127
+使用cl快照检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>同上</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>taskID小于等于0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>接口测试主要是测试C++驱动中的各个类的接口功能是否正常，主要验证两大操作：数据库操作和集群操作。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>兼容性测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>分别在windows linux上执行测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>验证所有测试用例和samples</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大小端测试（暂时无法测试）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动库测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>分别验证链接静态库 动态库执行测试</t>
+    <t>INT32 attachCollection ( const CHAR *subClFullName,
+                         const bson::BSONObj &amp;options)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用hint options构造bson
+3.调用query flag与FLG_QUERY_EXPLAIN做或运算</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.检查oid oid为NULL时生成OID
+3.使用cl全名 oid createMode构造bson
+4.构造打开lob消息
+5.发送 接收 解析 检查消息
+6.更新缓存
+7.构造lob对象返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+oid为NULL oid不为NULL
+检查返回的lob信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名 oid构造bson
+3.构造删除lob消息
+4.发送 接收 解析 检查消息
+5.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+oid未创建
+使用listLobs检查lob是否被删除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名 oid read模式构造bson
+3.构造打开lob消息
+4.发送 接收 解析 检查消息
+5.更新缓存
+6.构造lob对象（解析返回消息获取相关信息构造lob）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+oid未创建
+使用读取lob等操作检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名构造bson
+3.调用内部函数_runCmdOfLob
+4.检查cl全名 连接
+5.构造查询消息
+6.发送 接收 解析 检查消息
+7.更新缓存
+8.构造cursor返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+创建lob后使用listLobs检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查cl全名 连接
+2.使用cl全名构造bson
+2.构造查询消息
+3.发送 接收 解析 检查消息
+4.更新缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用create idIndex和options构造bson
+2.调用alterCollection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用listIndexes检查索引创建结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.使用drop idIndex和null构造bson
+2.调用alterCollection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查索引删除结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游标已关闭 连接断开
+返回大数据量的cursor，从第一条记录遍历到游标末尾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查游标是否关闭
+2.检查recvBuffer是否为空 连接是否正常，如果为空且连接正常，则发送getMore消息到服务端获取
+3.从reciveBuffer中获取记录，检查是否跳过边界，如果跳过边界且连接正常，则继续发送getMore消息获取；如果跳过边界且连接断开，则返回已到集合末尾；如果未跳过边界，则构造bson记录返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游标已关闭 连接断开
+检查返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查游标 上下文 连接
+2.构造杀死上下文的消息
+3.发送 接收 解析 检查消息
+4.将游标的contextID置为-1 状态置为关闭
+4.将游标从连接 集合上反注册</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复关闭游标 连接断开
+使游标先于连接 集合析构（未使用close做反注册）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接 检查节点的主机名端口号
+2.创建sdb对象，调用sdb的connect( hostname, svcname )并返回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>node未创建 连接断开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.调用内部函数_stopStart
+2.检查连接 hostname svcname
+3.使用hostname svcname构造bson
+4.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.检查连接
+2.使用rgname构造bson
+3.调用getList
+4.从游标中获取结果返回
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开
+检查返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接
+2.调用getDetail获取组的详细信息
+3.从组的详细信息中找到主节点信息
+4.使用主节点的信息构造node对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开
+数据组无主
+检查返回结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接
+2.调用getDetail获取组的详细信息
+3.从组的详细信息中找到非主节点的信息，放入vector
+4.从vector中随机取值构造node，如果vector为空，则获取主节点的信息构造node</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开
+数据组一个节点 多个节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接 空指针
+2.将pNodeName按:分隔成hostname svcname
+3.调用getNode( pHostName, pServiceName, node )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开 空指针
+pNodeName非法节点名
+（字符串中没有:分隔主机名和端口号）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接 空指针
+2.调用getDetail获取组信息
+3.从组信息中获取匹配的节点
+4.构造node对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开 空指针
+获取存在的节点 不存在的节点 检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接 rgname 空指针
+2.使用rgname hostname svcnmae dbpath和options构造bson（options过滤前面参数的字段）
+3.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针
+2.使用rgname hostname svcname和configure构造bson(configure过滤与前面参数重名的字段)
+3.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">连接断开 rg对象未创建 空指针
+options包含数据组名 主机名 端口号 路径且与前面的参数有冲突（正常，被剔除） 
+创建不存在的节点
+创建已存在的节点 使用getNode检查结果
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">连接断开 rg对象未创建 空指针
+options包含数据组名 主机名 端口号 路径且与前面的参数有冲突（正常，被剔除）
+删除不存在的节点
+删除存在的节点
+使用getNode检查结果
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开 rg对象未创建</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接 rgname
+2.使用rgname构造bson
+2.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查连接
+2.使用rgname构造bson
+3.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查rgname 连接
+2.检查空指针
+3.将hostame svcname 和options中的onlyAttach字段合并成一个bson对象
+4.runCommand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开 rg对象未创建
+空指针
+options中onlyAttach字段分别为true/false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开 rg对象未创建
+空指针
+options中onlyDetach字段分别为true/false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.检查domainname 连接
+2.使用domainname options构造bson
+3.runCommand
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain对象未创建 连接断开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查domainname 连接
+2.使用domainname构造bson
+3.调用getList</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob对象未创建 lob已关闭 连接断开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查lob 连接
+2.构造lob关闭消息
+3.发送 接收 解析 检查消息
+4.将lob对象的成员置为无效</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.检查lob 连接
+2.检查空指针
+3.检查lob打开模式 len=0
+4.检查是否已读到lob末尾
+5.从lob的buffer中读取直到读到需要读取的长度，或者读到lob末尾
+6.返回buf和read
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob对象未创建 lob关闭 连接断开
+空指针
+打开模式为create
+len等于0 超过lob大小
+读到lob末尾后继续读取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.检查lob 连接
+2.检查空指针
+3.检查lob打开模式 len=0
+4.每次最多写入2M大小内容，检查len的长度，超过2M时分批按2M发送，小于2M时直接发送
+5.构造lob写消息
+6.发送 接收 解析 检查消息
+7.更新lob大小
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob对象未创建 lob关闭 连接断开
+空指针 len=0
+打开模式为read
+写入内容小于2M 大于2M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查lob 连接
+2.检查lob打开模式
+3.根据size和whence做lob偏移，超过边界时报错</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob对象未创建 lob关闭 连接断开
+lob打开模式为create
+size和whence组合超出边界</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.检查空指针
+2.设置缓存策略（是否开启缓存 缓存间隔时间）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空指针
+开启缓存 不开启缓存</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接断开后获取集合
+空指针 集合全名长度超过255
+创建集合并获取 获取不存在的集合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用closeAllCursors后检查游标 lob操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 空串
+切分后查询cl快照检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl对象未创建 连接断开
+空指针 空串
+百分比小于0 或者 大于100
+切分后查询cl快照检查结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.调用内部函数_queryAndModify
+2.检查update参数
+2.将update returnNew update操作名合并成一个modify的bson，将hint和modify合并成一个bson
+3.flag值与FLG_QUERY_MODIFY做或运算
+4.调用query</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">flag覆盖所有取值和一个非法值
+      <t xml:space="preserve">update参数为空
+flag覆盖一个合法值和一个非法值
+returnNew覆盖true/false
+检查结果
 </t>
     </r>
     <r>
@@ -1620,778 +2601,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>0</t>
+      <t/>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_FORCE_HINT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_PARALLED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_WITH_RETURNDATA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-QUERY_PREPARE_MORE
-QUERY_KEEP_SHARDINGKEY_IN_UPDATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-numToReturn取值为1（与flag组合验证）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">update为空对象
-hint不为空对象
-flag覆盖所有取值和一个非法值
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_FORCE_HINT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_PARALLED
-QUERY_WITH_RETURNDATA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-QUERY_PREPARE_MORE
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>QUERY_KEEP_SHARDINGKEY_IN_UPDATE</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sortBufferSize小于0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT32 getQueryMeta ( sdbCursor &amp;cursor,
-                     const bson::BSONObj &amp;condition,
-                     const bson::BSONObj &amp;orderBy,
-                     const bson::BSONObj &amp;hint,
-                     INT64 numToSkip,
-                     INT64 numToReturn )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>游标已关闭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pNodeName非法节点名
-（字符串中没有:分隔主机名和端口号）
-不存在节点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">options包含数据组名 主机名 端口号 路径且与前面的参数有冲突（正常，被剔除） </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>options包含数据组名、主机名、端口号、OnlyAttach且与前面的参数冲突（驱动中未剔除，但是bson遍历按先后添加顺序）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上（OnlyAttach改成OnlyDetach）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复关闭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>打开模式为create的lob
-关闭lob后读取
-len等于0 超过lob大小 普通值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>打开模式为read的lob
-关闭lob后写
-len等于0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>百分比小于0 或者 大于100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>接口测试重点：1、验证接口正常的功能（覆盖默认值参数校验）
-             2、参数校验：指针类型参数检查空指针，字符串类型参数校验空串，vector类型参数检验空vector，数组长度参数校验小于等于0
-                         集合空间名 集合名 数据组名 域名校验最大长度127
-                         经过驱动处理的参数进行校验，覆盖驱动参数处理的每一个分支
-             3、与sdb shell对应的接口比较，检查多余的参数
-             4、验证sdb shell中不存在的接口的功能( resetSnapshot/getQueryMeta/Lob )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、验证正常功能测试时没有内存泄露
-2、验证并发测试时无内存泄露
-3、验证大小端测试时没有内存泄露
-4、验证samples中的内存泄露
-5、验证获取多个游标后，不使用接口断开连接，使用析构断开连接时的资源泄露</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常功能测试：测试接口的正常功能
-异常功能测试：连接断开后执行操作
-             对象未创建执行操作
-             对象关闭后执行操作（游标Lob）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>options中含有Alter不含有Alter字段
-Alter合法使用：{ Alter:{}, Option:{} }
-              { Alter:{} }
-文档中的options没有Alter字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C++驱动测试设计
-C++驱动的主要功能是与数据库引擎进行通信，一般的流程是校验传入参数后构造消息发送到引擎端，然后接收引擎返回的消息进行解析返回结果给客户端。对于C++驱动接口的测试主要针对接口的功能和参数校验进行测试。由于同一个连接上的对象共用套接字（驱动无锁），不能对同一个连接上的对象进行并发操作，连接之间没有共用的资源，不做并发测试。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数校验</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上
-isDeleteCurrent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>检查返回结果的oid是否正确
-插入不是4字节对齐的bson
-obj带oid 不带oid</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合法oid
-不合法oid(非24字节长度的16进制字符串,构造OID时core)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>游标已关闭
-遍历到游标末尾
-obj不为空
-返回大数据量的cursor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>flag覆盖所有取值和一个非法值
-0
-UPDATE_KEEP_SHARDINGKEY
-setOnInsert不为默认值 hint不为默认值
-setOnInsert不为默认值 hint为默认值
-setOnInsert为默认值 hint不为默认值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">打开模式为create的lob
-关闭lob后seek
-whence覆盖所有取值和一个非法值
-SDB_LOB_SEEK_SET
-SDB_LOB_SEEK_CUR
-SDB_LOB_SEEK_END
-size和whence组合超过边界，边界内值
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT32 connect ( const CHAR *pHostName,
-                 const CHAR *pServiceName )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调用connect( pHostName, port, "", "")</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调用connect( pHostName, pServiceName, "", "")</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.将pServiceName转换为端口号，服务名转换，转换数字
-2.调用connect( pHostName, port, pUsrName, pPasswd)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查参数 空指针检查
-2.密码转换为md5
-3.构造鉴权消息并发送，接收返回消息，检查返回消息有效性（opCode）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.空指针检查
-2.密码转换md5
-3.构造删除鉴权消息并发送，接收返回消息，检查返回消息有效性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复断开连接</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.如果scoket还存在，则断开（构造连接断开消息并发送，关闭并释放scoket）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.将listType映射为对应的命令
-2.构造查询消息并发送，接收并检查返回消息
-3.构造cursor对象返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>断开连接后执行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>连接断开后获取集合
-空指针 集合全名长度超过255
-创建集合并获取 获取不存在的集合
-获取集合时内存不足</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>连接断开后获取cs
-空指针 cs名长度超过127
-创建cs并获取 获取不存在的cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查socket
-2.检查空指针 cs名长度
-3.从本地缓存中获取cs，如果获取失败则从服务端获取(runCommand)，并新建缓存插入
-4.构造cs对象返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查socket是否连接
-2.检查空指针 集合全名长度
-3.从本地缓存中获取集合，如果获取失败则发送查询消息到服务端获取集合(runCommand)，并将集合插入缓存中（缓存为一个哈希表，表内每个节点存储名字和时间）
-4.构造cl对象并返回（指定cl对应的db name）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs名字长度超过127 空指针</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查cs名字长度（未检查空指针）
-2.构造bson，加入csname字段，再加入options的所有字段
-2.runCommand（消息构造发送接收检查）
-3.构造cs对象
-4.插入缓存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查cs名字长度（未检查空指针）
-2.runCommand（消息构造发送接收检查）
-3.构造cs对象
-4.插入缓存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pServiceName验证服务名/端口/空指针</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>pConnAddrs中的地址没有使用:分割主机名 端口号/空指针
-arrSize取值为0或负数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查参数 空指针检查 arrSize&lt;=0
-2.循环获取地址数组内的随机值，将地址按:分隔成主机名和端口号，调用connect( pHostName, pServiceName, pUsrName, pPasswd )进行连接，当连接成功后退出返回连接成功，或者两次循环产生相同的随机值时退出返回连接失败</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查cs名字长度
-2.构造bson，加入cs名字
-3.runCommand
-4.删除缓存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs名字长度超过127 空指针
-删除cs后获取cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">调用getList </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针
-2.使用rgname构造cond，然后调用getList
-3.获取游标中的第一个元素，使用元素内容构造rg对象( rgname rgid db isCatalog ）
-4.如果游标为空，返回失败</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-获取不存在的rg
-获取数据组 编目组，检查组信息（组名 组ID 是否编目组）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用id构造cond，调用getList
-2.以下步骤同上</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取不存在的rg
-获取数据组 编目组，检查组信息（组名 组ID 是否编目组）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查rgname长度
-2.runCommand
-3.构造rg对象返回，将rg添加到db的set中（注册）（cs cl操作中没有注册操作）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rg名长度超过127 空指针</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 检查长度=0 &gt;127
-2.runCommand （没有反注册操作）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rg名长度等于0 超过127 空指针
-使rg先于db进行析构</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针
-2.构造bson，加入hostname svcname dbpath，再加入config的各个字段，config中的字段与前面参数重复时跳过这些字段
-3.runCommand</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-config中包含了hostname svcname dbpath且与前面参数不一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查rgname长度
-2.构造bson，加入rgname
-3.runCommand
-4.构造rg对象，注册</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查sql语句合法性（第一个非空字符是否是s S l L）
-2.构造sql消息
-3.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-sql语句不合法（字符串以s S l L开头）
-合法的sql更新语句应该是update …</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查sql语句合法性（第一个非空字符是否是s S l L）
-2.构造sql消息
-3.发送 接收 解析 检查消息
-4.构造cursor对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.将snapType映射为对应的命令(switch)
-2.构造查询消息并发送，接收检查返回消息
-3.构造cursor对象并返回（设置cursor的成员值）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查socket是否连接
-2.构造查询消息并发送，接收并检查返回消息（调用runCommand）（runCommand用于处理查询消息）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-sql语句不合法（字符串不以s S l L开头）
-合法的sql查询语句应该是select .. 或 list ..</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.构造开始事务消息
-2.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.构造提交事务消息
-2.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.构造回滚事务消息
-2.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.构造查询消息
-2.发送 接收 解析 检查消息（可以使用runCommand）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用spname构造bson
-2.构造查询消息
-3.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针
-2.使用code构造bson
-3.构造查询消息
-4.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用code构造bson
-2.构造查询消息
-3.发送 接收 解析 检查消息
-4.构造cursor对象
-5.检查返回消息的返回个数 长度等，给type赋值（errmsg无用参数）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用options构造bson（多余的拷贝）
-2.构造查询消息
-3.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上
-最后构造cursor返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上 不需要构造cursor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 检查num &lt; 0
-2.使用taskIDs构造bson
-3.构造查询消息
-4.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-num小于等于0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查taskID&lt;=0
-2.使用taskID构造bson
-3.构造查询消息
-4.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>options为空对象
-options的第一个字段不是PreferInstance
-options中的PreferInstance的值非法或者类型非法
-合法值m M s S a A 1-7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查options是否为空
-2.找到options的第一个字段，检查是否是PreferInstance，并且字段值是否合法，使用该字段构造bson
-3.构造查询消息
-4.发送 接收 解析 检查消息</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调用closeAllCursors后检查游标 lob操作</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.构造杀死所有上下文的消息并发送
-2.将连接的游标lob清空，各个游标lob对象上的连接置为NULL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>检查socket是否存在 是否连接状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>未创建的连接对象检查有效性
-创建连接后检查有效性
-断开连接后检查有效性</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针 domain名长度&gt;127</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 domain名长度
-2.构造bson 加入domainname
-3.runCommand</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 domain名长度
-2.构造bson 加入domainname和options
-3.runCommand
-4.构造domain对象返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 domain名长度
-2.构造bson 加入domainname
-3.调用getList，加入bson作为匹配条件
-4.从游标中获取结果，构造domain对象返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针 domain名长度&gt;127
-获取不存在的domain
-获取存在的domain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调用getList(hint无用参数)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>runCommand</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UINT64 getLastAliveTime() const</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回成员变量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用主机名 端口号创建scocket连接（如果socket已连接，则断开重连）；设置socket属性（disableNagle keepalive keepidle keepinterval keepcount）；如果使用ssl，并且有宏定义，使用ssl连接
-2.获取服务端系统信息（判断大小端）
-3.密码转换为md5
-4.构造鉴权消息发送，接收返回消息并校验（校验返回消息的opCode与发送消息的opCode是否对应，大小端转换）（消息构造的流程：计算消息包需要的4字节对齐长度，分配buffer，将消息内容按消息格式按4字节对齐拷贝入buffer中，大小端转换）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调用createCollection( pCollection, _staticObj, collection )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 cl名长度
-2.检查cs对象 连接
-3.从缓存中获取cl，获取失败时从服务端获取(使用集合全名构造bson然后runCommand)，插入缓存
-4.构造cl对象返回</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.检查空指针 cl名长度
-2.检查cs对象 连接
-3.使用集合全名构造bson然后runCommand
-4.构造cl对象，插入缓存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针 cl名长度&gt;127
-cs对象未创建 连接断开
-创建cl然后获取
-获取不存在的cl</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针 cl名长度&gt;127
-cs对象未创建 连接断开</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>空指针
-重复连接
-服务端关闭后检查连接有效性（节点正常重启，异常重启）
-开启SSL进行连接（驱动未开启SSL宏）
-客户端 服务端分别为大端 小端</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2403,7 +2614,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2458,19 +2669,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color indexed="81"/>
@@ -2486,26 +2684,27 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2691,11 +2890,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2724,10 +2920,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2736,13 +2938,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2750,9 +2949,36 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="58">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -3150,105 +3376,126 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C71" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:C71" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
   <autoFilter ref="A1:C71">
     <filterColumn colId="2"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" name="接口名" dataDxfId="48"/>
-    <tableColumn id="2" name="测试点" dataDxfId="47"/>
-    <tableColumn id="3" name="流程" dataDxfId="46"/>
+    <tableColumn id="1" name="接口名" dataDxfId="55"/>
+    <tableColumn id="2" name="测试点" dataDxfId="54"/>
+    <tableColumn id="3" name="流程" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C11" totalsRowShown="0" dataDxfId="45">
-  <autoFilter ref="A1:C11">
-    <filterColumn colId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C5" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+  <autoFilter ref="A1:C5">
+    <filterColumn colId="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" name="接口名" dataDxfId="44"/>
-    <tableColumn id="2" name="测试点" dataDxfId="43"/>
-    <tableColumn id="3" name="流程" dataDxfId="0"/>
+    <tableColumn id="1" name="接口名" dataDxfId="21"/>
+    <tableColumn id="3" name="测试点" dataDxfId="2"/>
+    <tableColumn id="2" name="流程" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:B42" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39">
-  <autoFilter ref="A1:B42"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="38"/>
-    <tableColumn id="2" name="参数校验" dataDxfId="37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C11" totalsRowShown="0" dataDxfId="52">
+  <autoFilter ref="A1:C11">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="51"/>
+    <tableColumn id="3" name="测试点" dataDxfId="7"/>
+    <tableColumn id="2" name="流程" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B4" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33">
-  <autoFilter ref="A1:B4"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="32"/>
-    <tableColumn id="2" name="参数校验" dataDxfId="31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C42" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46">
+  <autoFilter ref="A1:C42">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="45"/>
+    <tableColumn id="4" name="测试点" dataDxfId="6"/>
+    <tableColumn id="2" name="流程" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:B9" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
-  <autoFilter ref="A1:B9"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="26"/>
-    <tableColumn id="2" name="参数校验" dataDxfId="25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:C4" totalsRowShown="0" headerRowDxfId="43" dataDxfId="41" headerRowBorderDxfId="42" tableBorderDxfId="40">
+  <autoFilter ref="A1:C4">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="39"/>
+    <tableColumn id="3" name="测试点" dataDxfId="5"/>
+    <tableColumn id="2" name="流程" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:B20" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21">
-  <autoFilter ref="A1:B20"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="20"/>
-    <tableColumn id="2" name="功能" dataDxfId="19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C9" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34">
+  <autoFilter ref="A1:C9">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="33"/>
+    <tableColumn id="3" name="测试点" dataDxfId="4"/>
+    <tableColumn id="2" name="流程" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:B5" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15">
-  <autoFilter ref="A1:B5"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="14"/>
-    <tableColumn id="2" name="功能" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:C20" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
+  <autoFilter ref="A1:C20">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="27"/>
+    <tableColumn id="3" name="测试点" dataDxfId="3"/>
+    <tableColumn id="2" name="流程" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:B13" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
-  <autoFilter ref="A1:B13"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="8"/>
-    <tableColumn id="2" name="功能" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:C13" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16">
+  <autoFilter ref="A1:C13">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="15"/>
+    <tableColumn id="3" name="测试点" dataDxfId="1"/>
+    <tableColumn id="2" name="流程" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table92" displayName="Table92" ref="A1:B2" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3">
-  <autoFilter ref="A1:B2"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="接口名" dataDxfId="2"/>
-    <tableColumn id="2" name="功能" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table92" displayName="Table92" ref="A1:C2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+  <autoFilter ref="A1:C2">
+    <filterColumn colId="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="接口名" dataDxfId="9"/>
+    <tableColumn id="3" name="测试点" dataDxfId="0"/>
+    <tableColumn id="2" name="流程" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3554,147 +3801,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="58.5" customHeight="1">
-      <c r="A1" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="A1" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
     </row>
     <row r="2" spans="1:3" ht="21" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
+      <c r="A2" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
     </row>
     <row r="3" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="40"/>
+      <c r="A3" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+    </row>
+    <row r="5" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+    </row>
+    <row r="6" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A6" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42"/>
-    </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A5" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
-    </row>
-    <row r="6" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" ht="87.75" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
+      <c r="A7" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
     </row>
     <row r="8" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A8" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
+      <c r="A8" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="C10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="11" spans="1:3" ht="61.5" customHeight="1">
-      <c r="A11" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>282</v>
+      <c r="A11" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="27" customHeight="1">
-      <c r="A12" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>272</v>
+      <c r="A12" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="52.5" customHeight="1">
-      <c r="A13" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>12</v>
+      <c r="A13" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>11</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="84.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>303</v>
+        <v>9</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="29.25" customHeight="1">
-      <c r="A15" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="35" t="s">
+      <c r="A15" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="34" t="s">
         <v>285</v>
       </c>
+      <c r="C15" s="34" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A16" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>285</v>
+      <c r="A16" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="26.25" customHeight="1">
-      <c r="A17" s="35" t="s">
-        <v>274</v>
+      <c r="A17" s="34" t="s">
+        <v>272</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3860,100 +4107,132 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="52.25" customWidth="1"/>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
+    <col min="2" max="2" width="32.625" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="31.5" customHeight="1">
+        <v>365</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="70.5" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" customHeight="1">
+        <v>459</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="103.5" customHeight="1">
       <c r="A3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="113.25" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="98.25" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="48.75" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="B5" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.75" customHeight="1">
+      <c r="A6" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="98.25" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="23.25" customHeight="1">
+      <c r="A8" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="8"/>
-    </row>
-    <row r="7" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:3" ht="23.25" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="8"/>
-    </row>
-    <row r="8" spans="1:2" ht="23.25" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25.5" customHeight="1">
+      <c r="A10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9" spans="1:2" ht="23.25" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" ht="24" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="8"/>
-    </row>
-    <row r="10" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="24" customHeight="1">
+      <c r="A12" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="8"/>
-    </row>
-    <row r="11" spans="1:2" ht="24" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="12"/>
+    </row>
+    <row r="13" spans="1:3" ht="24" customHeight="1">
+      <c r="A13" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="8"/>
-    </row>
-    <row r="12" spans="1:2" ht="24" customHeight="1">
-      <c r="A12" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="12"/>
-    </row>
-    <row r="13" spans="1:2" ht="24" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>165</v>
-      </c>
       <c r="B13" s="12"/>
+      <c r="C13" s="12" t="s">
+        <v>405</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3966,26 +4245,35 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="52.25" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="29.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="20.25" customHeight="1">
+        <v>468</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="54" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="8"/>
+        <v>164</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>467</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4011,507 +4299,506 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="33"/>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+    </row>
+    <row r="6" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+    </row>
+    <row r="7" spans="1:6" ht="23.25" customHeight="1">
+      <c r="A7" s="33"/>
+      <c r="B7" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="F8" s="33"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="33"/>
+    </row>
+    <row r="10" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="33"/>
+    </row>
+    <row r="11" spans="1:6" ht="21" customHeight="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" s="33"/>
+    </row>
+    <row r="12" spans="1:6" ht="21" customHeight="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+    </row>
+    <row r="13" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="33"/>
+    </row>
+    <row r="15" spans="1:6" ht="22.5" customHeight="1">
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+    </row>
+    <row r="16" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17" s="33"/>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="33"/>
+    </row>
+    <row r="19" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A2" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="34"/>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="D4" s="34" t="s">
+      <c r="F19" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-    </row>
-    <row r="6" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-    </row>
-    <row r="7" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="F7" s="34" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="21" customHeight="1">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="22.5" customHeight="1">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A24" s="33"/>
+      <c r="B24" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" s="33"/>
+    </row>
+    <row r="25" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A25" s="33"/>
+      <c r="B25" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="33"/>
+    </row>
+    <row r="26" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A26" s="33"/>
+      <c r="B26" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="33"/>
+    </row>
+    <row r="27" spans="1:6" ht="21" customHeight="1">
+      <c r="A27" s="33"/>
+      <c r="B27" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18" customHeight="1">
+      <c r="A28" s="33"/>
+      <c r="B28" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="33"/>
+    </row>
+    <row r="29" spans="1:6" ht="17.25" customHeight="1">
+      <c r="A29" s="33"/>
+      <c r="B29" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="F29" s="33"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A30" s="33"/>
+      <c r="B30" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="33"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A31" s="33"/>
+      <c r="B31" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="E31" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A32" s="33"/>
+      <c r="B32" s="33" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="F8" s="34"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" s="34"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="F11" s="34"/>
-    </row>
-    <row r="12" spans="1:6" ht="21" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-    </row>
-    <row r="13" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="34"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="34"/>
-    </row>
-    <row r="15" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-    </row>
-    <row r="16" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="34" t="s">
+      <c r="C32" s="33"/>
+      <c r="E32" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="F32" s="33"/>
+    </row>
+    <row r="33" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A33" s="33"/>
+      <c r="B33" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="E33" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" s="33"/>
+    </row>
+    <row r="34" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A34" s="33"/>
+      <c r="B34" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="E34" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A35" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="E16" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="34"/>
-    </row>
-    <row r="19" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="34" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="F24" s="34"/>
-    </row>
-    <row r="25" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25" s="34"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" s="34"/>
-    </row>
-    <row r="27" spans="1:6" ht="21" customHeight="1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="F28" s="34"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F29" s="34"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="F30" s="34"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="C31" s="34"/>
-      <c r="E31" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="F31" s="34" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="C32" s="34"/>
-      <c r="E32" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="34"/>
-      <c r="E33" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="F33" s="34"/>
-    </row>
-    <row r="34" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="C34" s="34"/>
-      <c r="E34" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="F34" s="34" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A35" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="F35" s="34" t="s">
-        <v>171</v>
+      <c r="F35" s="33" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="F36" s="34"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="F36" s="33"/>
     </row>
     <row r="37" spans="1:6" ht="20.25" customHeight="1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="F37" s="34"/>
+      <c r="C37" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4524,6 +4811,7 @@
     <col min="1" max="1" width="76" customWidth="1"/>
     <col min="2" max="2" width="35.25" customWidth="1"/>
     <col min="3" max="3" width="43.875" customWidth="1"/>
+    <col min="4" max="4" width="34.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
@@ -4531,1077 +4819,864 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="37.5" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="174" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="55.5" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="69" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="91.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="61.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="66" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="41.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>324</v>
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="76.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="83.25" customHeight="1">
-      <c r="A11" s="29" t="s">
-        <v>268</v>
+      <c r="A11" s="28" t="s">
+        <v>266</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="54" customHeight="1">
-      <c r="A12" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>327</v>
+      <c r="A12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="80.25" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>266</v>
+      <c r="A13" s="28" t="s">
+        <v>264</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="80.25" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="36" customHeight="1">
+      <c r="A15" s="28" t="s">
         <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="36" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="108" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A17" s="28" t="s">
         <v>23</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="38.25" customHeight="1">
-      <c r="A17" s="29" t="s">
-        <v>24</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="72.75" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="48.75" customHeight="1">
+      <c r="A19" s="28" t="s">
         <v>25</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="48.75" customHeight="1">
-      <c r="A19" s="29" t="s">
-        <v>26</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="60.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="89.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="61.5" customHeight="1">
       <c r="A22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21" customHeight="1">
+      <c r="A23" s="27" t="s">
         <v>29</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="21" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>30</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="28.5" customHeight="1">
       <c r="A24" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="21.75" customHeight="1">
       <c r="A25" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
     </row>
     <row r="26" spans="1:3" ht="20.25" customHeight="1">
       <c r="A26" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1">
       <c r="A27" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
     </row>
     <row r="28" spans="1:3" ht="17.25" customHeight="1">
       <c r="A28" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="21" customHeight="1">
       <c r="A29" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
     </row>
     <row r="30" spans="1:3" ht="89.25" customHeight="1">
       <c r="A30" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1">
       <c r="A31" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="51.75" customHeight="1">
       <c r="A32" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="24" customHeight="1">
       <c r="A33" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="59.25" customHeight="1">
       <c r="A34" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="43.5" customHeight="1">
       <c r="A35" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="80.25" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="21.75" customHeight="1">
       <c r="A37" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
     </row>
     <row r="38" spans="1:3" ht="62.25" customHeight="1">
-      <c r="A38" s="27" t="s">
-        <v>276</v>
+      <c r="A38" s="43" t="s">
+        <v>274</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="72" customHeight="1">
       <c r="A39" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="33" customHeight="1">
       <c r="A40" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
     </row>
     <row r="41" spans="1:3" ht="73.5" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="37.5" customHeight="1">
       <c r="A42" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="22"/>
       <c r="C42" s="15" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="33.75" customHeight="1">
       <c r="A43" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="22"/>
       <c r="C43" s="15" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="31.5" customHeight="1">
       <c r="A44" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" s="22"/>
       <c r="C44" s="15" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="37.5" customHeight="1">
       <c r="A45" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" s="22"/>
       <c r="C45" s="15" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="64.5" customHeight="1">
       <c r="A46" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="51.75" customHeight="1">
       <c r="A47" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="21" customHeight="1">
       <c r="A48" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
     </row>
     <row r="49" spans="1:3" ht="30" customHeight="1">
       <c r="A49" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="64.5" customHeight="1">
       <c r="A50" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
     </row>
     <row r="51" spans="1:3" ht="84.75" customHeight="1">
       <c r="A51" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="22" t="s">
-        <v>364</v>
+        <v>69</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>363</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="53.25" customHeight="1">
       <c r="A52" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="22"/>
       <c r="C52" s="12" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="75" customHeight="1">
       <c r="A53" s="25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
     </row>
     <row r="54" spans="1:3" ht="80.25" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B54" s="22"/>
       <c r="C54" s="15" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="23.25" customHeight="1">
       <c r="A55" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="22" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="74.25" customHeight="1">
       <c r="A56" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
     </row>
     <row r="57" spans="1:3" ht="80.25" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" s="22"/>
       <c r="C57" s="22" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="62.25" customHeight="1">
       <c r="A58" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="70.5" customHeight="1">
       <c r="A59" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="91.5" customHeight="1">
       <c r="A60" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>373</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="45.75" customHeight="1">
       <c r="A61" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>374</v>
+        <v>471</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="19.5" customHeight="1">
       <c r="A62" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
     </row>
     <row r="63" spans="1:3" ht="45.75" customHeight="1">
       <c r="A63" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="63.75" customHeight="1">
       <c r="A64" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="54" customHeight="1">
       <c r="A65" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="65.25" customHeight="1">
       <c r="A66" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="78.75" customHeight="1">
       <c r="A67" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="22"/>
       <c r="C67" s="22" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="23.25" customHeight="1">
       <c r="A68" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
     </row>
     <row r="69" spans="1:3" ht="24" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="B69" s="22"/>
       <c r="C69" s="22" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="21.75" customHeight="1">
       <c r="A70" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B70" s="22"/>
       <c r="C70" s="22" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="24" customHeight="1">
       <c r="A71" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="22" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:C17"/>
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="70.25" customWidth="1"/>
-    <col min="2" max="2" width="35.125" customWidth="1"/>
-    <col min="3" max="3" width="35.25" customWidth="1"/>
+    <col min="1" max="1" width="61.375" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="31.5" customHeight="1">
-      <c r="A2" s="29" t="s">
-        <v>80</v>
+      <c r="B1" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" ht="92.25" customHeight="1">
+      <c r="C2" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="57.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>394</v>
+        <v>457</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" ht="81.75" customHeight="1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="55.5" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="32.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>457</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="33" customHeight="1">
-      <c r="A6" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3" ht="34.5" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="34.5" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" ht="19.5" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" ht="20.25" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" ht="29.25" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1"/>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:B42"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="82.375" customWidth="1"/>
-    <col min="2" max="2" width="51.875" customWidth="1"/>
+    <col min="1" max="1" width="70.25" customWidth="1"/>
+    <col min="2" max="2" width="25.25" customWidth="1"/>
+    <col min="3" max="3" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.5" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" ht="65.25" customHeight="1">
+      <c r="B1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31.5" customHeight="1">
+      <c r="A2" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="69.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" ht="51.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="76.5" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A4" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" ht="77.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" ht="63.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="64.5" customHeight="1">
+        <v>82</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="33" customHeight="1">
+      <c r="A6" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="28"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="34.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="33" customHeight="1">
+        <v>275</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="61.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" ht="52.5" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="64.5" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2" ht="96.75" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="42" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" spans="1:2" ht="117" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2" ht="132" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="108" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2" ht="150" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="123" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2" ht="72.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="1:2" ht="78.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="33.75" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" spans="1:2" ht="35.25" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="3"/>
-    </row>
-    <row r="22" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:2" ht="23.25" customHeight="1">
-      <c r="A23" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="20.25" customHeight="1">
+      <c r="A10" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2" ht="27" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="B10" s="28"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" ht="29.25" customHeight="1">
+      <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="1:2" ht="27" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:2" ht="38.25" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2" ht="39" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:2" ht="96.75" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2" ht="100.5" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" ht="38.25" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="15"/>
-    </row>
-    <row r="33" spans="1:2" ht="23.25" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="15"/>
-    </row>
-    <row r="34" spans="1:2" ht="141.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="15"/>
-    </row>
-    <row r="35" spans="1:2" ht="39" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="24" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="15"/>
-    </row>
-    <row r="37" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="15"/>
-    </row>
-    <row r="38" spans="1:2" ht="27" customHeight="1">
-      <c r="A38" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="15"/>
-    </row>
-    <row r="39" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="15"/>
-    </row>
-    <row r="40" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="15"/>
-    </row>
-    <row r="41" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="15"/>
-    </row>
-    <row r="42" spans="1:2" ht="19.5" customHeight="1">
-      <c r="A42" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B42" s="15"/>
-    </row>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5614,62 +5689,526 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="82.375" customWidth="1"/>
+    <col min="2" max="2" width="30.5" customWidth="1"/>
+    <col min="3" max="3" width="45.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="49.5" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="83.25" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="119.25" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="96" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="63.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="98.25" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="91.5" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="94.5" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="83.25" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="96.75" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="75.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="117" customHeight="1">
+      <c r="A13" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" ht="132" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="108" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="150" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="123" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="116.25" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="78.75" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A20" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" ht="111" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="81" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="23.25" customHeight="1">
+      <c r="A23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="27" customHeight="1">
+      <c r="A24" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="27" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="24.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A28" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" ht="78.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="96.75" customHeight="1">
+      <c r="A30" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" ht="100.5" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="86.25" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="54.75" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="141.75" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="113.25" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="84" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="96.75" customHeight="1">
+      <c r="A37" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="121.5" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="83.25" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="42.75" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="36.75" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="19.5" customHeight="1">
+      <c r="A42" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="25"/>
+      <c r="C42" s="15"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="41.375" customWidth="1"/>
-    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="31.625" customWidth="1"/>
+    <col min="3" max="3" width="37.375" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="41.375" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="63" customHeight="1">
+        <v>365</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="125.25" customHeight="1">
       <c r="A2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="43.5" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="79.5" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="25.5" customHeight="1">
-      <c r="A4" s="8" t="s">
-        <v>123</v>
-      </c>
       <c r="B4" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1"/>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:2" ht="18" customHeight="1"/>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:2" ht="15" customHeight="1"/>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:2">
+        <v>432</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1"/>
+    <row r="12" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:3" ht="18" customHeight="1"/>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:3" ht="15" customHeight="1"/>
+    <row r="16" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
     </row>
     <row r="34" ht="48" customHeight="1"/>
     <row r="35" ht="45.75" customHeight="1"/>
@@ -5696,225 +6235,102 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="40.25" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
-    <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" customWidth="1"/>
-    <col min="5" max="5" width="21.75" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="4" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
+    <col min="6" max="6" width="21.75" customWidth="1"/>
+    <col min="7" max="7" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="21" customHeight="1">
-      <c r="A2" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21" customHeight="1">
+      <c r="A2" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:3" ht="47.25" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="22.5" customHeight="1">
+      <c r="A4" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" spans="1:3" ht="24" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="8"/>
-    </row>
-    <row r="4" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.75" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5" spans="1:2" ht="24" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="8"/>
-    </row>
-    <row r="6" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="69.75" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="26.25" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="8"/>
-    </row>
-    <row r="7" spans="1:2" ht="21" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="8"/>
-    </row>
-    <row r="8" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A8" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>130</v>
-      </c>
       <c r="B9" s="8"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="71.75" customWidth="1"/>
-    <col min="2" max="2" width="34.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="40.5" customHeight="1">
-      <c r="A2" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="8"/>
-    </row>
-    <row r="4" spans="1:2" ht="24" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5" spans="1:2" ht="27.75" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="8"/>
-    </row>
-    <row r="6" spans="1:2" ht="21" customHeight="1">
-      <c r="A6" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="8"/>
-    </row>
-    <row r="7" spans="1:2" ht="26.25" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="8"/>
-    </row>
-    <row r="8" spans="1:2" ht="38.25" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="8"/>
-    </row>
-    <row r="9" spans="1:2" ht="56.25" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="48.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="8"/>
-    </row>
-    <row r="11" spans="1:2" ht="51.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" s="8"/>
-    </row>
-    <row r="12" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="8"/>
-    </row>
-    <row r="13" spans="1:2" ht="61.5" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="51.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="8"/>
-    </row>
-    <row r="16" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="8"/>
-    </row>
-    <row r="17" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="8"/>
-    </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B18" s="8"/>
-    </row>
-    <row r="19" spans="1:2" ht="60.75" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="53.25" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>297</v>
+      <c r="C9" s="8" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -5928,47 +6344,207 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:B6"/>
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="61.375" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.75" customWidth="1"/>
+    <col min="2" max="2" width="27.125" customWidth="1"/>
+    <col min="3" max="3" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" thickBot="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" ht="14.25" thickBot="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:2" ht="27.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" ht="32.25" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" ht="16.5" customHeight="1"/>
+      <c r="B1" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.5" customHeight="1">
+      <c r="A2" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:3" ht="61.5" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1">
+      <c r="A4" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" spans="1:3" ht="68.25" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" ht="103.5" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A8" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:3" ht="56.25" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="48.75" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" ht="61.5" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="68.25" customHeight="1">
+      <c r="A12" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" ht="99.75" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="107.25" customHeight="1">
+      <c r="A14" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="48" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="54" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.25" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="24.75" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="90" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="68.25" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
